--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5214,7 +5214,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>175</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5618,7 +5618,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>183</v>
       </c>
@@ -5633,13 +5633,13 @@
         <v>62</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5721,7 +5721,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>186</v>
       </c>
@@ -5736,13 +5736,13 @@
         <v>187</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>74</v>
@@ -6030,7 +6030,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>198</v>
       </c>
@@ -6045,13 +6045,13 @@
         <v>199</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6045,7 +6045,7 @@
         <v>199</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>75</v>
